--- a/verification/report-samples/driver-details.xlsx
+++ b/verification/report-samples/driver-details.xlsx
@@ -7,7 +7,7 @@
     <sheet sheetId="1" name="Report" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A1:$CF20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A1:$CF24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$12</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Gujjar Brother Transport — TEST DATA ONLY</t>
   </si>
@@ -26,7 +26,7 @@
     <t>Driver Details · TEST accounting period</t>
   </si>
   <si>
-    <t>2026-01-01 to 2026-12-31 · PKR · 2026-10-06T19:37:04.646+00:00</t>
+    <t>2026-01-01 to 2026-12-31 · PKR · 2026-10-11T16:34:23.361+00:00</t>
   </si>
   <si>
     <t>Selected authorized records</t>
@@ -59,40 +59,40 @@
     <t>Supplementary driver details</t>
   </si>
   <si>
-    <t>driver name</t>
-  </si>
-  <si>
-    <t>vehical no</t>
+    <t>Driver name</t>
+  </si>
+  <si>
+    <t>Vehicle number</t>
   </si>
   <si>
     <t>Sale</t>
   </si>
   <si>
-    <t>expense</t>
-  </si>
-  <si>
-    <t>profit</t>
-  </si>
-  <si>
-    <t>tool</t>
-  </si>
-  <si>
-    <t>punjab police challan</t>
-  </si>
-  <si>
-    <t>ave</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>cycle</t>
-  </si>
-  <si>
-    <t>Driver Cycle commision</t>
-  </si>
-  <si>
-    <t>remarks</t>
+    <t>Expense</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>Tolls</t>
+  </si>
+  <si>
+    <t>Punjab Police</t>
+  </si>
+  <si>
+    <t>Average (km/L)</t>
+  </si>
+  <si>
+    <t>Weight (tonnes)</t>
+  </si>
+  <si>
+    <t>Cycles</t>
+  </si>
+  <si>
+    <t>Driver cycle commission</t>
+  </si>
+  <si>
+    <t>Remarks</t>
   </si>
   <si>
     <t>Recorded operating result by trip</t>
@@ -102,6 +102,20 @@
   </si>
   <si>
     <t>Operating profit</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Driver signature</t>
+  </si>
+  <si>
+    <t>Authorized officer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature: __________________
+Name: ____________________
+Date: _____________________</t>
   </si>
   <si>
     <t>Supplementary output: the handwritten sheet defines requested information, not a complete printed template.</t>
@@ -613,7 +627,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CF20"/>
+  <dimension ref="A1:CF24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="84" width="1.35" customWidth="1"/>
@@ -1821,7 +1835,7 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -1909,184 +1923,452 @@
       <c r="CE17" s="7"/>
       <c r="CF17" s="7"/>
     </row>
-    <row r="19" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="19" ht="22" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
-      <c r="AB19" s="2"/>
-      <c r="AC19" s="2"/>
-      <c r="AD19" s="2"/>
-      <c r="AE19" s="2"/>
-      <c r="AF19" s="2"/>
-      <c r="AG19" s="2"/>
-      <c r="AH19" s="2"/>
-      <c r="AI19" s="2"/>
-      <c r="AJ19" s="2"/>
-      <c r="AK19" s="2"/>
-      <c r="AL19" s="2"/>
-      <c r="AM19" s="2"/>
-      <c r="AN19" s="2"/>
-      <c r="AO19" s="2"/>
-      <c r="AP19" s="2"/>
-      <c r="AQ19" s="2"/>
-      <c r="AR19" s="2"/>
-      <c r="AS19" s="2"/>
-      <c r="AT19" s="2"/>
-      <c r="AU19" s="2"/>
-      <c r="AV19" s="2"/>
-      <c r="AW19" s="2"/>
-      <c r="AX19" s="2"/>
-      <c r="AY19" s="2"/>
-      <c r="AZ19" s="2"/>
-      <c r="BA19" s="2"/>
-      <c r="BB19" s="2"/>
-      <c r="BC19" s="2"/>
-      <c r="BD19" s="2"/>
-      <c r="BE19" s="2"/>
-      <c r="BF19" s="2"/>
-      <c r="BG19" s="2"/>
-      <c r="BH19" s="2"/>
-      <c r="BI19" s="2"/>
-      <c r="BJ19" s="2"/>
-      <c r="BK19" s="2"/>
-      <c r="BL19" s="2"/>
-      <c r="BM19" s="2"/>
-      <c r="BN19" s="2"/>
-      <c r="BO19" s="2"/>
-      <c r="BP19" s="2"/>
-      <c r="BQ19" s="2"/>
-      <c r="BR19" s="2"/>
-      <c r="BS19" s="2"/>
-      <c r="BT19" s="2"/>
-      <c r="BU19" s="2"/>
-      <c r="BV19" s="2"/>
-      <c r="BW19" s="2"/>
-      <c r="BX19" s="2"/>
-      <c r="BY19" s="2"/>
-      <c r="BZ19" s="2"/>
-      <c r="CA19" s="2"/>
-      <c r="CB19" s="2"/>
-      <c r="CC19" s="2"/>
-      <c r="CD19" s="2"/>
-      <c r="CE19" s="2"/>
-      <c r="CF19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
+      <c r="AS19" s="3"/>
+      <c r="AT19" s="3"/>
+      <c r="AU19" s="3"/>
+      <c r="AV19" s="3"/>
+      <c r="AW19" s="3"/>
+      <c r="AX19" s="3"/>
+      <c r="AY19" s="3"/>
+      <c r="AZ19" s="3"/>
+      <c r="BA19" s="3"/>
+      <c r="BB19" s="3"/>
+      <c r="BC19" s="3"/>
+      <c r="BD19" s="3"/>
+      <c r="BE19" s="3"/>
+      <c r="BF19" s="3"/>
+      <c r="BG19" s="3"/>
+      <c r="BH19" s="3"/>
+      <c r="BI19" s="3"/>
+      <c r="BJ19" s="3"/>
+      <c r="BK19" s="3"/>
+      <c r="BL19" s="3"/>
+      <c r="BM19" s="3"/>
+      <c r="BN19" s="3"/>
+      <c r="BO19" s="3"/>
+      <c r="BP19" s="3"/>
+      <c r="BQ19" s="3"/>
+      <c r="BR19" s="3"/>
+      <c r="BS19" s="3"/>
+      <c r="BT19" s="3"/>
+      <c r="BU19" s="3"/>
+      <c r="BV19" s="3"/>
+      <c r="BW19" s="3"/>
+      <c r="BX19" s="3"/>
+      <c r="BY19" s="3"/>
+      <c r="BZ19" s="3"/>
+      <c r="CA19" s="3"/>
+      <c r="CB19" s="3"/>
+      <c r="CC19" s="3"/>
+      <c r="CD19" s="3"/>
+      <c r="CE19" s="3"/>
+      <c r="CF19" s="3"/>
     </row>
-    <row r="20" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="20" ht="45" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="2"/>
-      <c r="AB20" s="2"/>
-      <c r="AC20" s="2"/>
-      <c r="AD20" s="2"/>
-      <c r="AE20" s="2"/>
-      <c r="AF20" s="2"/>
-      <c r="AG20" s="2"/>
-      <c r="AH20" s="2"/>
-      <c r="AI20" s="2"/>
-      <c r="AJ20" s="2"/>
-      <c r="AK20" s="2"/>
-      <c r="AL20" s="2"/>
-      <c r="AM20" s="2"/>
-      <c r="AN20" s="2"/>
-      <c r="AO20" s="2"/>
-      <c r="AP20" s="2"/>
-      <c r="AQ20" s="2"/>
-      <c r="AR20" s="2"/>
-      <c r="AS20" s="2"/>
-      <c r="AT20" s="2"/>
-      <c r="AU20" s="2"/>
-      <c r="AV20" s="2"/>
-      <c r="AW20" s="2"/>
-      <c r="AX20" s="2"/>
-      <c r="AY20" s="2"/>
-      <c r="AZ20" s="2"/>
-      <c r="BA20" s="2"/>
-      <c r="BB20" s="2"/>
-      <c r="BC20" s="2"/>
-      <c r="BD20" s="2"/>
-      <c r="BE20" s="2"/>
-      <c r="BF20" s="2"/>
-      <c r="BG20" s="2"/>
-      <c r="BH20" s="2"/>
-      <c r="BI20" s="2"/>
-      <c r="BJ20" s="2"/>
-      <c r="BK20" s="2"/>
-      <c r="BL20" s="2"/>
-      <c r="BM20" s="2"/>
-      <c r="BN20" s="2"/>
-      <c r="BO20" s="2"/>
-      <c r="BP20" s="2"/>
-      <c r="BQ20" s="2"/>
-      <c r="BR20" s="2"/>
-      <c r="BS20" s="2"/>
-      <c r="BT20" s="2"/>
-      <c r="BU20" s="2"/>
-      <c r="BV20" s="2"/>
-      <c r="BW20" s="2"/>
-      <c r="BX20" s="2"/>
-      <c r="BY20" s="2"/>
-      <c r="BZ20" s="2"/>
-      <c r="CA20" s="2"/>
-      <c r="CB20" s="2"/>
-      <c r="CC20" s="2"/>
-      <c r="CD20" s="2"/>
-      <c r="CE20" s="2"/>
-      <c r="CF20" s="2"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="3"/>
+      <c r="AD20" s="3"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="3"/>
+      <c r="AG20" s="3"/>
+      <c r="AH20" s="3"/>
+      <c r="AI20" s="3"/>
+      <c r="AJ20" s="3"/>
+      <c r="AK20" s="3"/>
+      <c r="AL20" s="3"/>
+      <c r="AM20" s="3"/>
+      <c r="AN20" s="3"/>
+      <c r="AO20" s="3"/>
+      <c r="AP20" s="3"/>
+      <c r="AQ20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AR20" s="3"/>
+      <c r="AS20" s="3"/>
+      <c r="AT20" s="3"/>
+      <c r="AU20" s="3"/>
+      <c r="AV20" s="3"/>
+      <c r="AW20" s="3"/>
+      <c r="AX20" s="3"/>
+      <c r="AY20" s="3"/>
+      <c r="AZ20" s="3"/>
+      <c r="BA20" s="3"/>
+      <c r="BB20" s="3"/>
+      <c r="BC20" s="3"/>
+      <c r="BD20" s="3"/>
+      <c r="BE20" s="3"/>
+      <c r="BF20" s="3"/>
+      <c r="BG20" s="3"/>
+      <c r="BH20" s="3"/>
+      <c r="BI20" s="3"/>
+      <c r="BJ20" s="3"/>
+      <c r="BK20" s="3"/>
+      <c r="BL20" s="3"/>
+      <c r="BM20" s="3"/>
+      <c r="BN20" s="3"/>
+      <c r="BO20" s="3"/>
+      <c r="BP20" s="3"/>
+      <c r="BQ20" s="3"/>
+      <c r="BR20" s="3"/>
+      <c r="BS20" s="3"/>
+      <c r="BT20" s="3"/>
+      <c r="BU20" s="3"/>
+      <c r="BV20" s="3"/>
+      <c r="BW20" s="3"/>
+      <c r="BX20" s="3"/>
+      <c r="BY20" s="3"/>
+      <c r="BZ20" s="3"/>
+      <c r="CA20" s="3"/>
+      <c r="CB20" s="3"/>
+      <c r="CC20" s="3"/>
+      <c r="CD20" s="3"/>
+      <c r="CE20" s="3"/>
+      <c r="CF20" s="3"/>
+    </row>
+    <row r="21" ht="85" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="5"/>
+      <c r="AG21" s="5"/>
+      <c r="AH21" s="5"/>
+      <c r="AI21" s="5"/>
+      <c r="AJ21" s="5"/>
+      <c r="AK21" s="5"/>
+      <c r="AL21" s="5"/>
+      <c r="AM21" s="5"/>
+      <c r="AN21" s="5"/>
+      <c r="AO21" s="5"/>
+      <c r="AP21" s="5"/>
+      <c r="AQ21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR21" s="5"/>
+      <c r="AS21" s="5"/>
+      <c r="AT21" s="5"/>
+      <c r="AU21" s="5"/>
+      <c r="AV21" s="5"/>
+      <c r="AW21" s="5"/>
+      <c r="AX21" s="5"/>
+      <c r="AY21" s="5"/>
+      <c r="AZ21" s="5"/>
+      <c r="BA21" s="5"/>
+      <c r="BB21" s="5"/>
+      <c r="BC21" s="5"/>
+      <c r="BD21" s="5"/>
+      <c r="BE21" s="5"/>
+      <c r="BF21" s="5"/>
+      <c r="BG21" s="5"/>
+      <c r="BH21" s="5"/>
+      <c r="BI21" s="5"/>
+      <c r="BJ21" s="5"/>
+      <c r="BK21" s="5"/>
+      <c r="BL21" s="5"/>
+      <c r="BM21" s="5"/>
+      <c r="BN21" s="5"/>
+      <c r="BO21" s="5"/>
+      <c r="BP21" s="5"/>
+      <c r="BQ21" s="5"/>
+      <c r="BR21" s="5"/>
+      <c r="BS21" s="5"/>
+      <c r="BT21" s="5"/>
+      <c r="BU21" s="5"/>
+      <c r="BV21" s="5"/>
+      <c r="BW21" s="5"/>
+      <c r="BX21" s="5"/>
+      <c r="BY21" s="5"/>
+      <c r="BZ21" s="5"/>
+      <c r="CA21" s="5"/>
+      <c r="CB21" s="5"/>
+      <c r="CC21" s="5"/>
+      <c r="CD21" s="5"/>
+      <c r="CE21" s="5"/>
+      <c r="CF21" s="5"/>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2"/>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="2"/>
+      <c r="AC23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AE23" s="2"/>
+      <c r="AF23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="2"/>
+      <c r="AM23" s="2"/>
+      <c r="AN23" s="2"/>
+      <c r="AO23" s="2"/>
+      <c r="AP23" s="2"/>
+      <c r="AQ23" s="2"/>
+      <c r="AR23" s="2"/>
+      <c r="AS23" s="2"/>
+      <c r="AT23" s="2"/>
+      <c r="AU23" s="2"/>
+      <c r="AV23" s="2"/>
+      <c r="AW23" s="2"/>
+      <c r="AX23" s="2"/>
+      <c r="AY23" s="2"/>
+      <c r="AZ23" s="2"/>
+      <c r="BA23" s="2"/>
+      <c r="BB23" s="2"/>
+      <c r="BC23" s="2"/>
+      <c r="BD23" s="2"/>
+      <c r="BE23" s="2"/>
+      <c r="BF23" s="2"/>
+      <c r="BG23" s="2"/>
+      <c r="BH23" s="2"/>
+      <c r="BI23" s="2"/>
+      <c r="BJ23" s="2"/>
+      <c r="BK23" s="2"/>
+      <c r="BL23" s="2"/>
+      <c r="BM23" s="2"/>
+      <c r="BN23" s="2"/>
+      <c r="BO23" s="2"/>
+      <c r="BP23" s="2"/>
+      <c r="BQ23" s="2"/>
+      <c r="BR23" s="2"/>
+      <c r="BS23" s="2"/>
+      <c r="BT23" s="2"/>
+      <c r="BU23" s="2"/>
+      <c r="BV23" s="2"/>
+      <c r="BW23" s="2"/>
+      <c r="BX23" s="2"/>
+      <c r="BY23" s="2"/>
+      <c r="BZ23" s="2"/>
+      <c r="CA23" s="2"/>
+      <c r="CB23" s="2"/>
+      <c r="CC23" s="2"/>
+      <c r="CD23" s="2"/>
+      <c r="CE23" s="2"/>
+      <c r="CF23" s="2"/>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
+      <c r="AA24" s="2"/>
+      <c r="AB24" s="2"/>
+      <c r="AC24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AE24" s="2"/>
+      <c r="AF24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="2"/>
+      <c r="AM24" s="2"/>
+      <c r="AN24" s="2"/>
+      <c r="AO24" s="2"/>
+      <c r="AP24" s="2"/>
+      <c r="AQ24" s="2"/>
+      <c r="AR24" s="2"/>
+      <c r="AS24" s="2"/>
+      <c r="AT24" s="2"/>
+      <c r="AU24" s="2"/>
+      <c r="AV24" s="2"/>
+      <c r="AW24" s="2"/>
+      <c r="AX24" s="2"/>
+      <c r="AY24" s="2"/>
+      <c r="AZ24" s="2"/>
+      <c r="BA24" s="2"/>
+      <c r="BB24" s="2"/>
+      <c r="BC24" s="2"/>
+      <c r="BD24" s="2"/>
+      <c r="BE24" s="2"/>
+      <c r="BF24" s="2"/>
+      <c r="BG24" s="2"/>
+      <c r="BH24" s="2"/>
+      <c r="BI24" s="2"/>
+      <c r="BJ24" s="2"/>
+      <c r="BK24" s="2"/>
+      <c r="BL24" s="2"/>
+      <c r="BM24" s="2"/>
+      <c r="BN24" s="2"/>
+      <c r="BO24" s="2"/>
+      <c r="BP24" s="2"/>
+      <c r="BQ24" s="2"/>
+      <c r="BR24" s="2"/>
+      <c r="BS24" s="2"/>
+      <c r="BT24" s="2"/>
+      <c r="BU24" s="2"/>
+      <c r="BV24" s="2"/>
+      <c r="BW24" s="2"/>
+      <c r="BX24" s="2"/>
+      <c r="BY24" s="2"/>
+      <c r="BZ24" s="2"/>
+      <c r="CA24" s="2"/>
+      <c r="CB24" s="2"/>
+      <c r="CC24" s="2"/>
+      <c r="CD24" s="2"/>
+      <c r="CE24" s="2"/>
+      <c r="CF24" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="51">
     <mergeCell ref="A1:CF1"/>
     <mergeCell ref="A2:CF2"/>
     <mergeCell ref="A3:CF3"/>
@@ -2132,7 +2414,12 @@
     <mergeCell ref="A17:AP17"/>
     <mergeCell ref="AQ17:CF17"/>
     <mergeCell ref="A19:CF19"/>
-    <mergeCell ref="A20:CF20"/>
+    <mergeCell ref="A20:AP20"/>
+    <mergeCell ref="AQ20:CF20"/>
+    <mergeCell ref="A21:AP21"/>
+    <mergeCell ref="AQ21:CF21"/>
+    <mergeCell ref="A23:CF23"/>
+    <mergeCell ref="A24:CF24"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ17:CF17">
     <cfRule type="dataBar" priority="1">
@@ -2142,7 +2429,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{04B7D41B-90B3-40C5-8D7B-84440C1F79F3}</x14:id>
+          <x14:id>{710CC379-350F-4789-9310-E2644647DBEA}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2158,7 +2445,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{04B7D41B-90B3-40C5-8D7B-84440C1F79F3}">
+          <x14:cfRule type="dataBar" id="{710CC379-350F-4789-9310-E2644647DBEA}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0" axisPosition="middle">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
